--- a/data_lake/datos_diarios_preliminares/dt=2026-08-01/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-08-01/Temp-max-julio-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC5DE1A-9496-422B-8746-B16D53F83329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A33BA4E-1576-472F-9539-294CDA780E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9517,10 +9517,12 @@
       <c r="AH5" s="57">
         <v>31.5</v>
       </c>
-      <c r="AI5" s="57"/>
+      <c r="AI5" s="57">
+        <v>31.4</v>
+      </c>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9538,11 +9540,11 @@
       </c>
       <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v>31.063333333333336</v>
+        <v>31.0741935483871</v>
       </c>
       <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v>0.86596155732510738</v>
+        <v>0.8768217723788716</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9648,10 +9650,12 @@
       <c r="AH6" s="57">
         <v>30.9</v>
       </c>
-      <c r="AI6" s="57"/>
+      <c r="AI6" s="57">
+        <v>31</v>
+      </c>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9669,11 +9673,11 @@
       </c>
       <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v>30.606666666666666</v>
+        <v>30.619354838709675</v>
       </c>
       <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v>-4.7613730355674733E-2</v>
+        <v>-3.4925558312664862E-2</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9779,10 +9783,12 @@
       <c r="AH7" s="57">
         <v>36.799999999999997</v>
       </c>
-      <c r="AI7" s="57"/>
+      <c r="AI7" s="57">
+        <v>37.299999999999997</v>
+      </c>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>36.799999999999997</v>
+        <v>37.299999999999997</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
@@ -9800,11 +9806,11 @@
       </c>
       <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v>35.396666666666661</v>
+        <v>35.458064516129028</v>
       </c>
       <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v>2.0306506590975886</v>
+        <v>2.0920485085599552</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9910,10 +9916,12 @@
       <c r="AH8" s="57">
         <v>34.4</v>
       </c>
-      <c r="AI8" s="57"/>
+      <c r="AI8" s="57">
+        <v>34</v>
+      </c>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9931,11 +9939,11 @@
       </c>
       <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v>33.233333333333334</v>
+        <v>33.258064516129032</v>
       </c>
       <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v>0.98429032258064098</v>
+        <v>1.0090215053763387</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10041,10 +10049,12 @@
       <c r="AH9" s="57">
         <v>37.6</v>
       </c>
-      <c r="AI9" s="57"/>
+      <c r="AI9" s="57">
+        <v>35.700000000000003</v>
+      </c>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>37.6</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
@@ -10062,11 +10072,11 @@
       </c>
       <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v>34.066666666666663</v>
+        <v>34.119354838709668</v>
       </c>
       <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v>0.97542052898281639</v>
+        <v>1.0281087010258219</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10172,10 +10182,12 @@
       <c r="AH10" s="57">
         <v>37.299999999999997</v>
       </c>
-      <c r="AI10" s="57"/>
+      <c r="AI10" s="57">
+        <v>36.200000000000003</v>
+      </c>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>37.299999999999997</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -10193,11 +10205,11 @@
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v>35.976666666666659</v>
+        <v>35.983870967741929</v>
       </c>
       <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v>0.59642843900630282</v>
+        <v>0.60363274008157219</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10303,10 +10315,12 @@
       <c r="AH11" s="57">
         <v>41.2</v>
       </c>
-      <c r="AI11" s="57"/>
+      <c r="AI11" s="57">
+        <v>38.799999999999997</v>
+      </c>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>41.2</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
@@ -10324,11 +10338,11 @@
       </c>
       <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v>38.293333333333322</v>
+        <v>38.309677419354827</v>
       </c>
       <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v>2.756049240484721</v>
+        <v>2.7723933265062257</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10434,10 +10448,12 @@
       <c r="AH12" s="57">
         <v>36.200000000000003</v>
       </c>
-      <c r="AI12" s="57"/>
+      <c r="AI12" s="57">
+        <v>35.799999999999997</v>
+      </c>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>36.200000000000003</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10455,11 +10471,11 @@
       </c>
       <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v>34.700000000000003</v>
+        <v>34.735483870967741</v>
       </c>
       <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v>2.5113758538262658</v>
+        <v>2.5468597247940039</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10565,10 +10581,12 @@
       <c r="AH13" s="57">
         <v>37.6</v>
       </c>
-      <c r="AI13" s="57"/>
+      <c r="AI13" s="57">
+        <v>35.6</v>
+      </c>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10586,11 +10604,11 @@
       </c>
       <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v>35.386666666666663</v>
+        <v>35.393548387096772</v>
       </c>
       <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v>2.0048745519713265</v>
+        <v>2.0117562724014348</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10696,10 +10714,12 @@
       <c r="AH14" s="57">
         <v>36.6</v>
       </c>
-      <c r="AI14" s="57"/>
+      <c r="AI14" s="57">
+        <v>34.1</v>
+      </c>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>36.6</v>
+        <v>34.1</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10717,11 +10737,11 @@
       </c>
       <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v>34.746666666666663</v>
+        <v>34.725806451612897</v>
       </c>
       <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v>1.521730067452431</v>
+        <v>1.5008698523986652</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10827,10 +10847,12 @@
       <c r="AH15" s="57">
         <v>33.5</v>
       </c>
-      <c r="AI15" s="57"/>
+      <c r="AI15" s="57">
+        <v>31.3</v>
+      </c>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>33.5</v>
+        <v>31.3</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10848,11 +10870,11 @@
       </c>
       <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v>31.903333333333329</v>
+        <v>31.883870967741931</v>
       </c>
       <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v>0.16799587725337872</v>
+        <v>0.14853351166198081</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -11007,10 +11029,12 @@
       <c r="AH17" s="57">
         <v>36.200000000000003</v>
       </c>
-      <c r="AI17" s="57"/>
+      <c r="AI17" s="57">
+        <v>34.6</v>
+      </c>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>36.200000000000003</v>
+        <v>34.6</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -11028,11 +11052,11 @@
       </c>
       <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v>34.236666666666665</v>
+        <v>34.248387096774188</v>
       </c>
       <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v>1.5626844642195081</v>
+        <v>1.5744048943270315</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11138,10 +11162,12 @@
       <c r="AH18" s="57">
         <v>29.6</v>
       </c>
-      <c r="AI18" s="57"/>
+      <c r="AI18" s="57">
+        <v>28.9</v>
+      </c>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -11159,11 +11185,11 @@
       </c>
       <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v>27.960000000000012</v>
+        <v>27.99032258064517</v>
       </c>
       <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v>1.9001291460431418</v>
+        <v>1.9304517266883003</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11269,10 +11295,12 @@
       <c r="AH19" s="57">
         <v>34.799999999999997</v>
       </c>
-      <c r="AI19" s="57"/>
+      <c r="AI19" s="57">
+        <v>34.9</v>
+      </c>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>34.799999999999997</v>
+        <v>34.9</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -11290,11 +11318,11 @@
       </c>
       <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v>34.093333333333327</v>
+        <v>34.119354838709668</v>
       </c>
       <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v>0.84237093066368374</v>
+        <v>0.86839243604002547</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11400,7 +11428,9 @@
       <c r="AH20" s="57">
         <v>31.3</v>
       </c>
-      <c r="AI20" s="57"/>
+      <c r="AI20" s="57">
+        <v>31.3</v>
+      </c>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
         <v>31.3</v>
@@ -11421,11 +11451,11 @@
       </c>
       <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v>30.24666666666667</v>
+        <v>30.280645161290323</v>
       </c>
       <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v>1.6058620689655214</v>
+        <v>1.6398405635891748</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11531,10 +11561,12 @@
       <c r="AH21" s="57">
         <v>24.9</v>
       </c>
-      <c r="AI21" s="57"/>
+      <c r="AI21" s="57">
+        <v>24.8</v>
+      </c>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11552,11 +11584,11 @@
       </c>
       <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v>24.226666666666663</v>
+        <v>24.245161290322574</v>
       </c>
       <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v>1.6171635150166921</v>
+        <v>1.6356581386726035</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11730,7 +11762,9 @@
       <c r="AH23" s="57">
         <v>30.6</v>
       </c>
-      <c r="AI23" s="57"/>
+      <c r="AI23" s="57">
+        <v>30.6</v>
+      </c>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
         <v>30.6</v>
@@ -11751,11 +11785,11 @@
       </c>
       <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v>28.716666666666672</v>
+        <v>28.777419354838713</v>
       </c>
       <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v>1.8482795698924726</v>
+        <v>1.9090322580645136</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11861,10 +11895,12 @@
       <c r="AH24" s="57">
         <v>31.5</v>
       </c>
-      <c r="AI24" s="57"/>
+      <c r="AI24" s="57">
+        <v>32</v>
+      </c>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>32</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11882,11 +11918,11 @@
       </c>
       <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v>29.62</v>
+        <v>29.696774193548389</v>
       </c>
       <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v>1.3681758832565194</v>
+        <v>1.4449500768049077</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11992,10 +12028,12 @@
       <c r="AH25" s="57">
         <v>35.799999999999997</v>
       </c>
-      <c r="AI25" s="57"/>
+      <c r="AI25" s="57">
+        <v>35.1</v>
+      </c>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>35.799999999999997</v>
+        <v>35.1</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
@@ -12013,11 +12051,11 @@
       </c>
       <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v>32.603333333333339</v>
+        <v>32.683870967741939</v>
       </c>
       <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v>2.2274679401122697</v>
+        <v>2.3080055745208696</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12123,10 +12161,12 @@
       <c r="AH26" s="57">
         <v>20.2</v>
       </c>
-      <c r="AI26" s="57"/>
+      <c r="AI26" s="57">
+        <v>20.8</v>
+      </c>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -12144,11 +12184,11 @@
       </c>
       <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v>19.749333333333336</v>
+        <v>19.783225806451615</v>
       </c>
       <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v>1.2064617258899766</v>
+        <v>1.2403541990082552</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12252,10 +12292,12 @@
       <c r="AH27" s="57">
         <v>20.6</v>
       </c>
-      <c r="AI27" s="57"/>
+      <c r="AI27" s="57">
+        <v>20.2</v>
+      </c>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
@@ -12273,11 +12315,11 @@
       </c>
       <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v>19.193103448275863</v>
+        <v>19.22666666666667</v>
       </c>
       <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v>2.5110529041674745</v>
+        <v>2.5446161225582813</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12383,10 +12425,12 @@
       <c r="AH28" s="57">
         <v>33.299999999999997</v>
       </c>
-      <c r="AI28" s="57"/>
+      <c r="AI28" s="57">
+        <v>33.700000000000003</v>
+      </c>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>33.299999999999997</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -12404,11 +12448,11 @@
       </c>
       <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v>32.016666666666673</v>
+        <v>32.07096774193549</v>
       </c>
       <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v>1.4882140650105136</v>
+        <v>1.5425151402793311</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12580,10 +12624,12 @@
       <c r="AH30" s="57">
         <v>35.6</v>
       </c>
-      <c r="AI30" s="57"/>
+      <c r="AI30" s="57">
+        <v>36.200000000000003</v>
+      </c>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>35.6</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -12601,11 +12647,11 @@
       </c>
       <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v>35.03</v>
+        <v>35.067741935483873</v>
       </c>
       <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v>1.2877491039426516</v>
+        <v>1.3254910394265238</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12711,10 +12757,12 @@
       <c r="AH31" s="57">
         <v>27.6</v>
       </c>
-      <c r="AI31" s="57"/>
+      <c r="AI31" s="57">
+        <v>27.8</v>
+      </c>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -12732,11 +12780,11 @@
       </c>
       <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v>27.32</v>
+        <v>27.335483870967742</v>
       </c>
       <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v>1.932575162879381</v>
+        <v>1.9480590338471231</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12842,10 +12890,12 @@
       <c r="AH32" s="57">
         <v>17.399999999999999</v>
       </c>
-      <c r="AI32" s="57"/>
+      <c r="AI32" s="57">
+        <v>16.600000000000001</v>
+      </c>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>17.399999999999999</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12863,11 +12913,11 @@
       </c>
       <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v>17.786666666666669</v>
+        <v>17.748387096774195</v>
       </c>
       <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v>1.4571288934054181</v>
+        <v>1.4188493235129442</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12973,10 +13023,12 @@
       <c r="AH33" s="57">
         <v>15.6</v>
       </c>
-      <c r="AI33" s="57"/>
+      <c r="AI33" s="57">
+        <v>15.2</v>
+      </c>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12994,11 +13046,11 @@
       </c>
       <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v>15.613333333333335</v>
+        <v>15.600000000000001</v>
       </c>
       <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v>0.86872080088988568</v>
+        <v>0.85538746755655204</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -13156,10 +13208,12 @@
       <c r="AH35" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="AI35" s="57"/>
+      <c r="AI35" s="57">
+        <v>31.2</v>
+      </c>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>31.2</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -13177,11 +13231,11 @@
       </c>
       <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v>32.019999999999996</v>
+        <v>31.993548387096773</v>
       </c>
       <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v>0.94730414746543445</v>
+        <v>0.92085253456221139</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -13408,10 +13462,12 @@
       <c r="AH38" s="57">
         <v>33.200000000000003</v>
       </c>
-      <c r="AI38" s="57"/>
+      <c r="AI38" s="57">
+        <v>26.6</v>
+      </c>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>26.6</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -13429,11 +13485,11 @@
       </c>
       <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v>30.3</v>
+        <v>30.180645161290322</v>
       </c>
       <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v>0.27097377660741984</v>
+        <v>0.15161893789774084</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -13540,10 +13596,12 @@
       <c r="AH39" s="57">
         <v>34.4</v>
       </c>
-      <c r="AI39" s="57"/>
+      <c r="AI39" s="57">
+        <v>30.6</v>
+      </c>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>34.4</v>
+        <v>30.6</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -13561,11 +13619,11 @@
       </c>
       <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v>31.696666666666665</v>
+        <v>31.661290322580644</v>
       </c>
       <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v>0.85353355580274481</v>
+        <v>0.81815721171672351</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -13672,10 +13730,12 @@
       <c r="AH40" s="57">
         <v>31.8</v>
       </c>
-      <c r="AI40" s="57"/>
+      <c r="AI40" s="57">
+        <v>31.4</v>
+      </c>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>31.8</v>
+        <v>31.4</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -13693,11 +13753,11 @@
       </c>
       <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v>30.063333333333333</v>
+        <v>30.106451612903225</v>
       </c>
       <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v>1.1157849462365519</v>
+        <v>1.1589032258064442</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -13804,10 +13864,12 @@
       <c r="AH41" s="57">
         <v>32.200000000000003</v>
       </c>
-      <c r="AI41" s="57"/>
+      <c r="AI41" s="57">
+        <v>31.4</v>
+      </c>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>32.200000000000003</v>
+        <v>31.4</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -13825,11 +13887,11 @@
       </c>
       <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v>30.846666666666678</v>
+        <v>30.864516129032268</v>
       </c>
       <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v>1.4803584229390871</v>
+        <v>1.4982078853046765</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -13997,10 +14059,12 @@
       <c r="AH43" s="57">
         <v>33.4</v>
       </c>
-      <c r="AI43" s="57"/>
+      <c r="AI43" s="57">
+        <v>31.2</v>
+      </c>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
-        <v>33.4</v>
+        <v>31.2</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -14018,11 +14082,11 @@
       </c>
       <c r="AO43" s="23">
         <f t="shared" si="7"/>
-        <v>31.488888888888887</v>
+        <v>31.478571428571428</v>
       </c>
       <c r="AP43" s="23">
         <f t="shared" si="4"/>
-        <v>1.4278270609318966</v>
+        <v>1.4175096006144372</v>
       </c>
       <c r="AT43" s="15"/>
     </row>
@@ -14127,10 +14191,12 @@
       <c r="AH44" s="57">
         <v>30.4</v>
       </c>
-      <c r="AI44" s="57"/>
+      <c r="AI44" s="57">
+        <v>30.3</v>
+      </c>
       <c r="AJ44" s="37">
         <f t="shared" si="0"/>
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -14148,11 +14214,11 @@
       </c>
       <c r="AO44" s="23">
         <f t="shared" si="7"/>
-        <v>31.282758620689652</v>
+        <v>31.249999999999996</v>
       </c>
       <c r="AP44" s="23">
         <f t="shared" si="4"/>
-        <v>2.2395714153291912</v>
+        <v>2.2068127946395357</v>
       </c>
       <c r="AT44" s="15"/>
     </row>
@@ -14259,10 +14325,12 @@
       <c r="AH45" s="57">
         <v>28.8</v>
       </c>
-      <c r="AI45" s="57"/>
+      <c r="AI45" s="57">
+        <v>29.8</v>
+      </c>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>28.8</v>
+        <v>29.8</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -14280,11 +14348,11 @@
       </c>
       <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v>30.746666666666673</v>
+        <v>30.71612903225807</v>
       </c>
       <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v>1.200850273787843</v>
+        <v>1.1703126393792402</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -14530,10 +14598,12 @@
       <c r="AH48" s="57">
         <v>31.5</v>
       </c>
-      <c r="AI48" s="57"/>
+      <c r="AI48" s="57">
+        <v>32.700000000000003</v>
+      </c>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>31.5</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -14551,11 +14621,11 @@
       </c>
       <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v>30.83666666666667</v>
+        <v>30.896774193548392</v>
       </c>
       <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v>0.49413381123058997</v>
+        <v>0.55424133811231258</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27454,12 +27524,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -27469,6 +27533,12 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
